--- a/AtchisonRegime/Outputs/USA/USA_Value/df_regSummary_USA_Value.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Value/df_regSummary_USA_Value.xlsx
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>1.674763436267108</v>
+        <v>1.376336791123065</v>
       </c>
       <c r="H2" t="n">
-        <v>3.229643246726068</v>
+        <v>3.743228803862341</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.997547424664449</v>
+        <v>-11.1575823049267</v>
       </c>
       <c r="J2" t="n">
         <v>6.89263768827785</v>
       </c>
       <c r="K2" t="n">
-        <v>32.55813953488372</v>
+        <v>33.07692307692307</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1548793911144378</v>
+        <v>0.1233762685115819</v>
       </c>
       <c r="O2" t="n">
         <v>-0.01208145336572686</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4117360617158783</v>
+        <v>0.2542204487015984</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>7.2021582714579</v>
       </c>
       <c r="K3" t="n">
-        <v>20.15503875968992</v>
+        <v>20</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>7.17869308850433</v>
       </c>
       <c r="K4" t="n">
-        <v>22.48062015503876</v>
+        <v>22.30769230769231</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         <v>8.24611022911178</v>
       </c>
       <c r="K5" t="n">
-        <v>24.8062015503876</v>
+        <v>24.61538461538462</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
